--- a/Design/Excel/ET/Datas/Demo.xlsx
+++ b/Design/Excel/ET/Datas/Demo.xlsx
@@ -75,7 +75,7 @@
     <t>/apple</t>
   </si>
   <si>
-    <t>/apple_bad</t>
+    <t>/apple</t>
   </si>
 </sst>
 </file>
